--- a/artfynd/A 47589-2025 artfynd.xlsx
+++ b/artfynd/A 47589-2025 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>137370929</v>
       </c>
       <c r="B6" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370930</v>
       </c>
       <c r="B7" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370932</v>
       </c>
       <c r="B8" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370949</v>
       </c>
       <c r="B9" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370940</v>
       </c>
       <c r="B13" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137370948</v>
       </c>
       <c r="B14" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 47589-2025 artfynd.xlsx
+++ b/artfynd/A 47589-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370943</v>
       </c>
       <c r="B2" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370944</v>
       </c>
       <c r="B3" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370934</v>
       </c>
       <c r="B4" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370939</v>
       </c>
       <c r="B5" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370929</v>
       </c>
       <c r="B6" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370930</v>
       </c>
       <c r="B7" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370932</v>
       </c>
       <c r="B8" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370949</v>
       </c>
       <c r="B9" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370935</v>
       </c>
       <c r="B10" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370950</v>
       </c>
       <c r="B11" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370924</v>
       </c>
       <c r="B12" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370940</v>
       </c>
       <c r="B13" t="n">
-        <v>92389</v>
+        <v>92394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137370948</v>
       </c>
       <c r="B14" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137370936</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137370923</v>
       </c>
       <c r="B16" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137370925</v>
       </c>
       <c r="B17" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137370927</v>
       </c>
       <c r="B18" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137370942</v>
       </c>
       <c r="B19" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137370941</v>
       </c>
       <c r="B20" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137370926</v>
       </c>
       <c r="B21" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137370946</v>
       </c>
       <c r="B22" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137370928</v>
       </c>
       <c r="B23" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137370933</v>
       </c>
       <c r="B24" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137370922</v>
       </c>
       <c r="B25" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137370947</v>
       </c>
       <c r="B26" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137370938</v>
       </c>
       <c r="B27" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47589-2025 artfynd.xlsx
+++ b/artfynd/A 47589-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370943</v>
       </c>
       <c r="B2" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370944</v>
       </c>
       <c r="B3" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370934</v>
       </c>
       <c r="B4" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370939</v>
       </c>
       <c r="B5" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370929</v>
       </c>
       <c r="B6" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370930</v>
       </c>
       <c r="B7" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370932</v>
       </c>
       <c r="B8" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370949</v>
       </c>
       <c r="B9" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370935</v>
       </c>
       <c r="B10" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370950</v>
       </c>
       <c r="B11" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370924</v>
       </c>
       <c r="B12" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370940</v>
       </c>
       <c r="B13" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137370948</v>
       </c>
       <c r="B14" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137370936</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137370923</v>
       </c>
       <c r="B16" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137370925</v>
       </c>
       <c r="B17" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137370927</v>
       </c>
       <c r="B18" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137370942</v>
       </c>
       <c r="B19" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137370941</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137370926</v>
       </c>
       <c r="B21" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137370946</v>
       </c>
       <c r="B22" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137370928</v>
       </c>
       <c r="B23" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137370933</v>
       </c>
       <c r="B24" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137370922</v>
       </c>
       <c r="B25" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137370938</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47589-2025 artfynd.xlsx
+++ b/artfynd/A 47589-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370943</v>
       </c>
       <c r="B2" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370944</v>
       </c>
       <c r="B3" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370934</v>
       </c>
       <c r="B4" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370939</v>
       </c>
       <c r="B5" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370929</v>
       </c>
       <c r="B6" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370930</v>
       </c>
       <c r="B7" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370932</v>
       </c>
       <c r="B8" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370949</v>
       </c>
       <c r="B9" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370935</v>
       </c>
       <c r="B10" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370950</v>
       </c>
       <c r="B11" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370924</v>
       </c>
       <c r="B12" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370940</v>
       </c>
       <c r="B13" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137370948</v>
       </c>
       <c r="B14" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137370936</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137370923</v>
       </c>
       <c r="B16" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137370925</v>
       </c>
       <c r="B17" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137370927</v>
       </c>
       <c r="B18" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137370942</v>
       </c>
       <c r="B19" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137370941</v>
       </c>
       <c r="B20" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137370926</v>
       </c>
       <c r="B21" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137370946</v>
       </c>
       <c r="B22" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137370928</v>
       </c>
       <c r="B23" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137370933</v>
       </c>
       <c r="B24" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137370922</v>
       </c>
       <c r="B25" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137370938</v>
       </c>
       <c r="B27" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47589-2025 artfynd.xlsx
+++ b/artfynd/A 47589-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370943</v>
       </c>
       <c r="B2" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370944</v>
       </c>
       <c r="B3" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370934</v>
       </c>
       <c r="B4" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370939</v>
       </c>
       <c r="B5" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370929</v>
       </c>
       <c r="B6" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370930</v>
       </c>
       <c r="B7" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370932</v>
       </c>
       <c r="B8" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370949</v>
       </c>
       <c r="B9" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370935</v>
       </c>
       <c r="B10" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370950</v>
       </c>
       <c r="B11" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370924</v>
       </c>
       <c r="B12" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370940</v>
       </c>
       <c r="B13" t="n">
-        <v>92407</v>
+        <v>92410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137370948</v>
       </c>
       <c r="B14" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137370936</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137370923</v>
       </c>
       <c r="B16" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137370925</v>
       </c>
       <c r="B17" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137370927</v>
       </c>
       <c r="B18" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137370942</v>
       </c>
       <c r="B19" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137370941</v>
       </c>
       <c r="B20" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137370926</v>
       </c>
       <c r="B21" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137370946</v>
       </c>
       <c r="B22" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137370928</v>
       </c>
       <c r="B23" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137370933</v>
       </c>
       <c r="B24" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137370922</v>
       </c>
       <c r="B25" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137370938</v>
       </c>
       <c r="B27" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47589-2025 artfynd.xlsx
+++ b/artfynd/A 47589-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370943</v>
       </c>
       <c r="B2" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370944</v>
       </c>
       <c r="B3" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370934</v>
       </c>
       <c r="B4" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370939</v>
       </c>
       <c r="B5" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370929</v>
       </c>
       <c r="B6" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370930</v>
       </c>
       <c r="B7" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370932</v>
       </c>
       <c r="B8" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370949</v>
       </c>
       <c r="B9" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370935</v>
       </c>
       <c r="B10" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370950</v>
       </c>
       <c r="B11" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370924</v>
       </c>
       <c r="B12" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370940</v>
       </c>
       <c r="B13" t="n">
-        <v>92410</v>
+        <v>92414</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137370948</v>
       </c>
       <c r="B14" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137370936</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137370923</v>
       </c>
       <c r="B16" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137370925</v>
       </c>
       <c r="B17" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137370927</v>
       </c>
       <c r="B18" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137370942</v>
       </c>
       <c r="B19" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137370941</v>
       </c>
       <c r="B20" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137370926</v>
       </c>
       <c r="B21" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137370946</v>
       </c>
       <c r="B22" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137370928</v>
       </c>
       <c r="B23" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137370933</v>
       </c>
       <c r="B24" t="n">
-        <v>80662</v>
+        <v>80666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137370922</v>
       </c>
       <c r="B25" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137370947</v>
       </c>
       <c r="B26" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>137370938</v>
       </c>
       <c r="B27" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
